--- a/assets/constructions/examples/ctd_tge_radial_sub.xlsx
+++ b/assets/constructions/examples/ctd_tge_radial_sub.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL6"/>
+  <dimension ref="A1:AP6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -619,46 +619,70 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SALHER 1010 M07</t>
+          <t>QS-SMALL103XHP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PALBIT</t>
+          <t>SANDVIK</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SAL</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>CoroCutⓇ XS QS shank tool for parting and grooving</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>COR_MAL3_H</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PALBIT</t>
+          <t>SANDVIK</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>SAL…R</t>
+          <t>CoroCut XS -size 3L (MACL 3 200-N)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ISO_5610:10X10</t>
+          <t>COR_QS_HP:15.785X15.875</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>PALB_SAL..R</t>
+          <t>COR_MACL3H</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -666,52 +690,46 @@
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>28</v>
+      </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R2" t="n">
-        <v>10</v>
+        <v>15.875</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15.875</v>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2</v>
-      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="n">
-        <v>10</v>
+        <v>15.875</v>
       </c>
       <c r="AC2" t="n">
-        <v>10</v>
+        <v>15.875</v>
       </c>
       <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="n">
-        <v>2</v>
-      </c>
+      <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="n">
         <v>4</v>
@@ -722,66 +740,74 @@
           <t>Steel</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr"/>
+      <c r="AJ2" t="n">
+        <v>0.154</v>
+      </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2022/ palbit основной каталог.pdf</t>
-        </is>
-      </c>
+          <t>2021/www.sandvik.coromant.com</t>
+        </is>
+      </c>
+      <c r="AM2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STEL1010-85</t>
+          <t>SALHER 1212 M07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VARGUS</t>
+          <t>PALBIT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ST-Cut</t>
+          <t>SAL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>VARGUS</t>
+          <t>PALBIT</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>6</v>
       </c>
-      <c r="G3" t="n">
-        <v>17</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>SAL…R</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ISO_5610:10X10</t>
+          <t>ISO_5610:12X12</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>VARGUS_ST:85L</t>
+          <t>PALB_SAL..R</t>
         </is>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -791,32 +817,36 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
+      <c r="Y3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2</v>
+      </c>
       <c r="AB3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AC3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="b">
         <v>0</v>
@@ -836,14 +866,28 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2022 / ST-Cut.pdf</t>
-        </is>
+          <t>2022/ palbit основной каталог.pdf</t>
+        </is>
+      </c>
+      <c r="AM3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>147.83</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AP3" t="n">
+        <v>13590.56</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STER0810-85</t>
+          <t>STEL375-85</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -871,12 +915,12 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ISO_5610:10X8</t>
+          <t>ISO_5610:9.525X9.525</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>VARGUS_ST:85R</t>
+          <t>VARGUS_ST:85L</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -889,7 +933,7 @@
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -899,15 +943,15 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>8</v>
+        <v>9.525</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>9.525</v>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>110</v>
+        <v>114.3</v>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
@@ -915,10 +959,10 @@
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
-        <v>8</v>
+        <v>9.525</v>
       </c>
       <c r="AC4" t="n">
-        <v>10</v>
+        <v>9.525</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
@@ -946,76 +990,98 @@
         <is>
           <t>2022 / ST-Cut.pdf</t>
         </is>
+      </c>
+      <c r="AM4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>151.41</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AP4" t="n">
+        <v>13919.68</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STESL1212-85T40</t>
+          <t>QS-SMALR2020X3HP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VARGUS</t>
+          <t>SANDVIK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ST-Cut</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>CoroCutⓇ XS QS shank tool for parting and grooving</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>COR_MAR3_H</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>VARGUS</t>
+          <t>SANDVIK</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G5" t="n">
-        <v>17</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>7.254</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>CoroCut XS -size 3R (MACR 3 200-N)</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ISO_5610:12X12</t>
+          <t>ISO_5610:20X20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>VARGUS_ST:85L</t>
+          <t>COR_MACR3H</t>
         </is>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>25</v>
+      </c>
+      <c r="N5" t="n">
+        <v>45</v>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R5" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>127</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
@@ -1023,19 +1089,15 @@
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>7.5</v>
+        <v>20</v>
       </c>
       <c r="AC5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="b">
         <v>1</v>
-      </c>
-      <c r="AF5" t="b">
-        <v>0</v>
       </c>
       <c r="AG5" t="n">
         <v>4</v>
@@ -1046,61 +1108,69 @@
           <t>Steel</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr"/>
+      <c r="AJ5" t="n">
+        <v>0.24</v>
+      </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2022 / ST-Cut.pdf</t>
-        </is>
-      </c>
+          <t>2021/www.sandvik.coromant.com</t>
+        </is>
+      </c>
+      <c r="AM5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SALHEL 2020 M07</t>
+          <t>STESL1010-85T30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PALBIT</t>
+          <t>VARGUS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SAL</t>
+          <t>ST-Cut</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PALBIT</t>
+          <t>VARGUS</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>6</v>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>SAL…L</t>
-        </is>
-      </c>
+      <c r="G6" t="n">
+        <v>17</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ISO_5610:20X20</t>
+          <t>ISO_5610:10X10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>PALB_SAL..L</t>
+          <t>VARGUS_ST:85L</t>
         </is>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
@@ -1115,36 +1185,32 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2</v>
-      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="n">
-        <v>20</v>
+        <v>7.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AD6" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
       <c r="AE6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF6" t="b">
         <v>0</v>
@@ -1164,8 +1230,22 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2022/ palbit основной каталог.pdf</t>
-        </is>
+          <t>2022 / ST-Cut.pdf</t>
+        </is>
+      </c>
+      <c r="AM6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>164.25</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AP6" t="n">
+        <v>15100.11</v>
       </c>
     </row>
   </sheetData>
